--- a/data_lake/bart_temp_med/dt=2026-09-20/temperaturamed.xlsx
+++ b/data_lake/bart_temp_med/dt=2026-09-20/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73255FDD-54DC-487A-A526-1793A5D5FA0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1546A38-D3AF-40FC-903B-7A4BE2E66DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6353,8 +6353,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="168" width="32.42578125" style="50" customWidth="1"/>
-    <col min="169" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="169" width="32.42578125" style="50" customWidth="1"/>
+    <col min="170" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6691,7 +6691,9 @@
       <c r="AB5" s="56">
         <v>30</v>
       </c>
-      <c r="AC5" s="56"/>
+      <c r="AC5" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AD5" s="56"/>
       <c r="AE5" s="56"/>
       <c r="AF5" s="56"/>
@@ -6706,11 +6708,11 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ5" s="71">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
-        <v>29.722222222222221</v>
+        <v>29.726315789473681</v>
       </c>
       <c r="AR5" s="71">
         <f>IFERROR(VLOOKUP(A5,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6718,7 +6720,7 @@
       </c>
       <c r="AS5" s="71">
         <f t="shared" ref="AS5:AS68" si="2">IF(OR(AQ5="",AR5=""),"",IFERROR(AQ5-AR5,""))</f>
-        <v>1.5266245105469309</v>
+        <v>1.5307180777983902</v>
       </c>
     </row>
     <row r="6" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6806,7 +6808,9 @@
       <c r="AB6" s="56">
         <v>30</v>
       </c>
-      <c r="AC6" s="56"/>
+      <c r="AC6" s="56">
+        <v>30.3</v>
+      </c>
       <c r="AD6" s="56"/>
       <c r="AE6" s="56"/>
       <c r="AF6" s="56"/>
@@ -6821,11 +6825,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>29.833333333333332</v>
+        <v>29.857894736842102</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6833,7 +6837,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>1.5816985507246422</v>
+        <v>1.6062599542334119</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6921,7 +6925,9 @@
       <c r="AB7" s="56">
         <v>32.5</v>
       </c>
-      <c r="AC7" s="56"/>
+      <c r="AC7" s="56">
+        <v>29.7</v>
+      </c>
       <c r="AD7" s="56"/>
       <c r="AE7" s="56"/>
       <c r="AF7" s="56"/>
@@ -6936,11 +6942,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>31.205555555555552</v>
+        <v>31.126315789473683</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6948,7 +6954,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>2.6157566226044615</v>
+        <v>2.5365168565225922</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7151,7 +7157,9 @@
       <c r="AB9" s="56">
         <v>32.5</v>
       </c>
-      <c r="AC9" s="56"/>
+      <c r="AC9" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AD9" s="56"/>
       <c r="AE9" s="56"/>
       <c r="AF9" s="56"/>
@@ -7166,11 +7174,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>30.366666666666667</v>
+        <v>30.273684210526319</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7178,7 +7186,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>0.67040598290601849</v>
+        <v>0.57742352676567066</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7266,7 +7274,9 @@
       <c r="AB10" s="56">
         <v>33.1</v>
       </c>
-      <c r="AC10" s="56"/>
+      <c r="AC10" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AD10" s="56"/>
       <c r="AE10" s="56"/>
       <c r="AF10" s="56"/>
@@ -7281,11 +7291,11 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v>32.150000000000006</v>
+        <v>31.968421052631584</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7293,7 +7303,7 @@
       </c>
       <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v>3.4286141542160848</v>
+        <v>3.2470352068476629</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7381,7 +7391,9 @@
       <c r="AB11" s="56">
         <v>33.700000000000003</v>
       </c>
-      <c r="AC11" s="56"/>
+      <c r="AC11" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AD11" s="56"/>
       <c r="AE11" s="56"/>
       <c r="AF11" s="56"/>
@@ -7396,11 +7408,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>32.477777777777774</v>
+        <v>32.336842105263152</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7408,7 +7420,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>4.2634899071400341</v>
+        <v>4.1225542346254116</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7611,7 +7623,9 @@
       <c r="AB13" s="56">
         <v>32.4</v>
       </c>
-      <c r="AC13" s="56"/>
+      <c r="AC13" s="56">
+        <v>26.9</v>
+      </c>
       <c r="AD13" s="56"/>
       <c r="AE13" s="56"/>
       <c r="AF13" s="56"/>
@@ -7626,11 +7640,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>30.661111111111111</v>
+        <v>30.463157894736838</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7638,7 +7652,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>2.8396682898288503</v>
+        <v>2.6417150734545771</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7726,7 +7740,9 @@
       <c r="AB14" s="56">
         <v>24.1</v>
       </c>
-      <c r="AC14" s="56"/>
+      <c r="AC14" s="56">
+        <v>23.8</v>
+      </c>
       <c r="AD14" s="56"/>
       <c r="AE14" s="56"/>
       <c r="AF14" s="56"/>
@@ -7741,11 +7757,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.916666666666671</v>
+        <v>23.910526315789479</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7753,7 +7769,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>2.2714743589743698</v>
+        <v>2.2653340080971773</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7841,7 +7857,9 @@
       <c r="AB15" s="56">
         <v>32.4</v>
       </c>
-      <c r="AC15" s="56"/>
+      <c r="AC15" s="56">
+        <v>32</v>
+      </c>
       <c r="AD15" s="56"/>
       <c r="AE15" s="56"/>
       <c r="AF15" s="56"/>
@@ -7856,11 +7874,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>31.038888888888884</v>
+        <v>31.089473684210521</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7868,7 +7886,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>2.3177047413793233</v>
+        <v>2.36828953670096</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7956,7 +7974,9 @@
       <c r="AB16" s="56">
         <v>29</v>
       </c>
-      <c r="AC16" s="56"/>
+      <c r="AC16" s="56">
+        <v>28.6</v>
+      </c>
       <c r="AD16" s="56"/>
       <c r="AE16" s="56"/>
       <c r="AF16" s="56"/>
@@ -7971,11 +7991,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>28.688888888888894</v>
+        <v>28.684210526315795</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7983,7 +8003,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>1.2764878671775222</v>
+        <v>1.2718095046044233</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8071,7 +8091,9 @@
       <c r="AB17" s="56">
         <v>26.9</v>
       </c>
-      <c r="AC17" s="56"/>
+      <c r="AC17" s="56">
+        <v>24</v>
+      </c>
       <c r="AD17" s="56"/>
       <c r="AE17" s="56"/>
       <c r="AF17" s="56"/>
@@ -8086,11 +8108,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>25.633333333333336</v>
+        <v>25.547368421052635</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8098,7 +8120,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>2.430836412151077</v>
+        <v>2.3448714998703757</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8186,7 +8208,9 @@
       <c r="AB18" s="56">
         <v>19.8</v>
       </c>
-      <c r="AC18" s="56"/>
+      <c r="AC18" s="56">
+        <v>18.399999999999999</v>
+      </c>
       <c r="AD18" s="56"/>
       <c r="AE18" s="56"/>
       <c r="AF18" s="56"/>
@@ -8201,11 +8225,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>19.466666666666669</v>
+        <v>19.410526315789475</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8213,7 +8237,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>2.2482686781609296</v>
+        <v>2.1921283272837364</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8301,7 +8325,9 @@
       <c r="AB19" s="56">
         <v>26.3</v>
       </c>
-      <c r="AC19" s="56"/>
+      <c r="AC19" s="56">
+        <v>25.1</v>
+      </c>
       <c r="AD19" s="56"/>
       <c r="AE19" s="56"/>
       <c r="AF19" s="56"/>
@@ -8316,11 +8342,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>24.927777777777781</v>
+        <v>24.93684210526316</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8328,7 +8354,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>2.9818803418803519</v>
+        <v>2.9909446693657316</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8416,7 +8442,9 @@
       <c r="AB20" s="56">
         <v>26.3</v>
       </c>
-      <c r="AC20" s="56"/>
+      <c r="AC20" s="56">
+        <v>25</v>
+      </c>
       <c r="AD20" s="56"/>
       <c r="AE20" s="56"/>
       <c r="AF20" s="56"/>
@@ -8431,11 +8459,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>25.261111111111116</v>
+        <v>25.247368421052638</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8443,7 +8471,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>3.1422932192328865</v>
+        <v>3.128550529174408</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8531,7 +8559,9 @@
       <c r="AB21" s="56">
         <v>30</v>
       </c>
-      <c r="AC21" s="56"/>
+      <c r="AC21" s="56">
+        <v>29.5</v>
+      </c>
       <c r="AD21" s="56"/>
       <c r="AE21" s="56"/>
       <c r="AF21" s="56"/>
@@ -8546,11 +8576,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>28.622222222222224</v>
+        <v>28.668421052631583</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8558,7 +8588,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>3.681177170035685</v>
+        <v>3.7273760004450445</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8646,7 +8676,9 @@
       <c r="AB22" s="56">
         <v>15.2</v>
       </c>
-      <c r="AC22" s="56"/>
+      <c r="AC22" s="56">
+        <v>16.100000000000001</v>
+      </c>
       <c r="AD22" s="56"/>
       <c r="AE22" s="56"/>
       <c r="AF22" s="56"/>
@@ -8661,11 +8693,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>15.661111111111106</v>
+        <v>15.684210526315786</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8673,7 +8705,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>1.8914000147362255</v>
+        <v>1.9144994299409053</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8761,7 +8793,9 @@
       <c r="AB23" s="56">
         <v>27.2</v>
       </c>
-      <c r="AC23" s="56"/>
+      <c r="AC23" s="56">
+        <v>27.5</v>
+      </c>
       <c r="AD23" s="56"/>
       <c r="AE23" s="56"/>
       <c r="AF23" s="56"/>
@@ -8776,11 +8810,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>26.977777777777771</v>
+        <v>27.005263157894731</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8876,7 +8910,9 @@
       <c r="AB24" s="56">
         <v>32.4</v>
       </c>
-      <c r="AC24" s="56"/>
+      <c r="AC24" s="56">
+        <v>31.1</v>
+      </c>
       <c r="AD24" s="56"/>
       <c r="AE24" s="56"/>
       <c r="AF24" s="56"/>
@@ -8891,11 +8927,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>31.116666666666667</v>
+        <v>31.115789473684213</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8903,7 +8939,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.7940961047254262</v>
+        <v>1.7932189117429722</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8991,7 +9027,9 @@
       <c r="AB25" s="56">
         <v>23.6</v>
       </c>
-      <c r="AC25" s="56"/>
+      <c r="AC25" s="56">
+        <v>22.5</v>
+      </c>
       <c r="AD25" s="56"/>
       <c r="AE25" s="56"/>
       <c r="AF25" s="56"/>
@@ -9006,11 +9044,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>23.211111111111109</v>
+        <v>23.173684210526314</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9018,7 +9056,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>3.216532595205468</v>
+        <v>3.1791056946206737</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9106,7 +9144,9 @@
       <c r="AB26" s="56">
         <v>11.7</v>
       </c>
-      <c r="AC26" s="56"/>
+      <c r="AC26" s="56">
+        <v>11.3</v>
+      </c>
       <c r="AD26" s="56"/>
       <c r="AE26" s="56"/>
       <c r="AF26" s="56"/>
@@ -9121,11 +9161,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>11.472222222222221</v>
+        <v>11.463157894736842</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9133,7 +9173,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>0.75475308641977179</v>
+        <v>0.74568875893439213</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9221,7 +9261,9 @@
       <c r="AB27" s="56">
         <v>28.1</v>
       </c>
-      <c r="AC27" s="56"/>
+      <c r="AC27" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AD27" s="56"/>
       <c r="AE27" s="56"/>
       <c r="AF27" s="56"/>
@@ -9236,11 +9278,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>27.761111111111109</v>
+        <v>27.789473684210527</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9248,7 +9290,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.0517988505747304</v>
+        <v>1.0801614236741486</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9334,7 +9376,9 @@
       <c r="AB28" s="56">
         <v>29.4</v>
       </c>
-      <c r="AC28" s="56"/>
+      <c r="AC28" s="56">
+        <v>28.7</v>
+      </c>
       <c r="AD28" s="56"/>
       <c r="AE28" s="56"/>
       <c r="AF28" s="56"/>
@@ -9349,11 +9393,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>27.8</v>
+        <v>27.85</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9361,7 +9405,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>1.1765434775216015</v>
+        <v>1.2265434775216022</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9449,7 +9493,9 @@
       <c r="AB29" s="56">
         <v>26.6</v>
       </c>
-      <c r="AC29" s="56"/>
+      <c r="AC29" s="56">
+        <v>27.1</v>
+      </c>
       <c r="AD29" s="56"/>
       <c r="AE29" s="56"/>
       <c r="AF29" s="56"/>
@@ -9464,11 +9510,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>28.727777777777778</v>
+        <v>28.642105263157898</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9476,7 +9522,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>0.82071531198688774</v>
+        <v>0.73504279736700795</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9564,7 +9610,9 @@
       <c r="AB30" s="56">
         <v>24.7</v>
       </c>
-      <c r="AC30" s="56"/>
+      <c r="AC30" s="56">
+        <v>25.3</v>
+      </c>
       <c r="AD30" s="56"/>
       <c r="AE30" s="56"/>
       <c r="AF30" s="56"/>
@@ -9579,11 +9627,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>26.072222222222219</v>
+        <v>26.03157894736842</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9591,7 +9639,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>0.25286332408511925</v>
+        <v>0.21222004923131976</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9679,7 +9727,9 @@
       <c r="AB31" s="98">
         <v>28.2</v>
       </c>
-      <c r="AC31" s="98"/>
+      <c r="AC31" s="98">
+        <v>27.1</v>
+      </c>
       <c r="AD31" s="98"/>
       <c r="AE31" s="98"/>
       <c r="AF31" s="98"/>
@@ -9694,11 +9744,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>27.788888888888891</v>
+        <v>27.752631578947373</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9706,7 +9756,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.4132213064713106</v>
+        <v>1.376963996529792</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9794,7 +9844,9 @@
       <c r="AB32" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="AC32" s="56"/>
+      <c r="AC32" s="56">
+        <v>20.93333333333333</v>
+      </c>
       <c r="AD32" s="56"/>
       <c r="AE32" s="56"/>
       <c r="AF32" s="56"/>
@@ -9809,11 +9861,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>20.527777777777779</v>
+        <v>20.549122807017543</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9821,7 +9873,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>3.0462188492648679</v>
+        <v>3.0675638785046324</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9909,7 +9961,9 @@
       <c r="AB33" s="56">
         <v>28.4</v>
       </c>
-      <c r="AC33" s="56"/>
+      <c r="AC33" s="56">
+        <v>28.95</v>
+      </c>
       <c r="AD33" s="56"/>
       <c r="AE33" s="56"/>
       <c r="AF33" s="56"/>
@@ -9924,11 +9978,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>28.350000000000005</v>
+        <v>28.381578947368428</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9936,7 +9990,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.6673021574530438</v>
+        <v>1.6988811048214671</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10024,7 +10078,9 @@
       <c r="AB34" s="56">
         <v>22</v>
       </c>
-      <c r="AC34" s="56"/>
+      <c r="AC34" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="AD34" s="56"/>
       <c r="AE34" s="56"/>
       <c r="AF34" s="56"/>
@@ -10039,11 +10095,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>21.87777777777778</v>
+        <v>21.8</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10051,7 +10107,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>2.1384854890562686</v>
+        <v>2.0607077112784893</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10139,7 +10195,9 @@
       <c r="AB35" s="56">
         <v>25.65</v>
       </c>
-      <c r="AC35" s="56"/>
+      <c r="AC35" s="56">
+        <v>23.65</v>
+      </c>
       <c r="AD35" s="56"/>
       <c r="AE35" s="56"/>
       <c r="AF35" s="56"/>
@@ -10154,11 +10212,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>25.405555555555551</v>
+        <v>25.31315789473684</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10166,7 +10224,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>1.5139598527964608</v>
+        <v>1.421562191977749</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10254,7 +10312,9 @@
       <c r="AB36" s="56">
         <v>21</v>
       </c>
-      <c r="AC36" s="56"/>
+      <c r="AC36" s="56">
+        <v>18.3</v>
+      </c>
       <c r="AD36" s="56"/>
       <c r="AE36" s="56"/>
       <c r="AF36" s="56"/>
@@ -10269,11 +10329,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>19.947222222222216</v>
+        <v>19.860526315789468</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10281,7 +10341,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.432868556879825</v>
+        <v>1.3461726504470768</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10369,7 +10429,9 @@
       <c r="AB37" s="56">
         <v>28.5</v>
       </c>
-      <c r="AC37" s="56"/>
+      <c r="AC37" s="56">
+        <v>27.9</v>
+      </c>
       <c r="AD37" s="56"/>
       <c r="AE37" s="56"/>
       <c r="AF37" s="56"/>
@@ -10384,11 +10446,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>28.269444444444442</v>
+        <v>28.25</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10396,7 +10458,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>2.4365205938697514</v>
+        <v>2.4170761494253092</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10484,7 +10546,9 @@
       <c r="AB38" s="56">
         <v>17</v>
       </c>
-      <c r="AC38" s="56"/>
+      <c r="AC38" s="56">
+        <v>15.35</v>
+      </c>
       <c r="AD38" s="56"/>
       <c r="AE38" s="56"/>
       <c r="AF38" s="56"/>
@@ -10499,11 +10563,11 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>16.455555555555556</v>
+        <v>16.397368421052633</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10511,7 +10575,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>1.4821685823754951</v>
+        <v>1.4239814478725723</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10599,7 +10663,9 @@
       <c r="AB39" s="56">
         <v>24.2</v>
       </c>
-      <c r="AC39" s="56"/>
+      <c r="AC39" s="56">
+        <v>21</v>
+      </c>
       <c r="AD39" s="56"/>
       <c r="AE39" s="56"/>
       <c r="AF39" s="56"/>
@@ -10614,11 +10680,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>22.792592592592591</v>
+        <v>22.698245614035088</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10708,7 +10774,9 @@
       <c r="AB40" s="56">
         <v>27.2</v>
       </c>
-      <c r="AC40" s="56"/>
+      <c r="AC40" s="56">
+        <v>23</v>
+      </c>
       <c r="AD40" s="56"/>
       <c r="AE40" s="56"/>
       <c r="AF40" s="56"/>
@@ -10723,11 +10791,11 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ40" s="71">
         <f t="shared" si="1"/>
-        <v>25.351111111111113</v>
+        <v>25.204166666666669</v>
       </c>
       <c r="AR40" s="71">
         <f>IFERROR(VLOOKUP(A40,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10735,7 +10803,7 @@
       </c>
       <c r="AS40" s="71">
         <f t="shared" si="2"/>
-        <v>2.925537738197292</v>
+        <v>2.7785932937528486</v>
       </c>
     </row>
     <row r="41" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10938,7 +11006,9 @@
       <c r="AB42" s="56">
         <v>28.5</v>
       </c>
-      <c r="AC42" s="56"/>
+      <c r="AC42" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AD42" s="56"/>
       <c r="AE42" s="56"/>
       <c r="AF42" s="56"/>
@@ -10953,11 +11023,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.99861111111111</v>
+        <v>27.980263157894736</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10965,7 +11035,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.70553639846744076</v>
+        <v>0.68718844525106704</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11053,7 +11123,9 @@
       <c r="AB43" s="56">
         <v>29.75</v>
       </c>
-      <c r="AC43" s="56"/>
+      <c r="AC43" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AD43" s="56"/>
       <c r="AE43" s="56"/>
       <c r="AF43" s="56"/>
@@ -11068,11 +11140,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>29.152777777777779</v>
+        <v>29.068421052631578</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11168,7 +11240,9 @@
       <c r="AB44" s="56">
         <v>28.824999999999999</v>
       </c>
-      <c r="AC44" s="56"/>
+      <c r="AC44" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AD44" s="56"/>
       <c r="AE44" s="56"/>
       <c r="AF44" s="56"/>
@@ -11183,11 +11257,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>28.390277777777776</v>
+        <v>28.346052631578942</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11195,7 +11269,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>1.1188760490786365</v>
+        <v>1.074650902879803</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11398,7 +11472,9 @@
       <c r="AB46" s="56">
         <v>28.8</v>
       </c>
-      <c r="AC46" s="56"/>
+      <c r="AC46" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AD46" s="56"/>
       <c r="AE46" s="56"/>
       <c r="AF46" s="56"/>
@@ -11413,11 +11489,11 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ46" s="71">
         <f t="shared" si="1"/>
-        <v>28.605555555555554</v>
+        <v>28.542105263157893</v>
       </c>
       <c r="AR46" s="71">
         <f>IFERROR(VLOOKUP(A46,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11425,7 +11501,7 @@
       </c>
       <c r="AS46" s="71">
         <f t="shared" si="2"/>
-        <v>1.1030114258347048</v>
+        <v>1.0395611334370436</v>
       </c>
     </row>
     <row r="47" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11780,7 +11856,9 @@
       <c r="AB50" s="56">
         <v>29.8</v>
       </c>
-      <c r="AC50" s="56"/>
+      <c r="AC50" s="56">
+        <v>25.75</v>
+      </c>
       <c r="AD50" s="56"/>
       <c r="AE50" s="56"/>
       <c r="AF50" s="56"/>
@@ -11795,11 +11873,11 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>28.430555555555557</v>
+        <v>28.289473684210527</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11807,7 +11885,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>1.3260420473524057</v>
+        <v>1.184960176007376</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12168,7 +12246,9 @@
       <c r="AB54" s="56">
         <v>31.6</v>
       </c>
-      <c r="AC54" s="56"/>
+      <c r="AC54" s="56">
+        <v>26</v>
+      </c>
       <c r="AD54" s="56"/>
       <c r="AE54" s="56"/>
       <c r="AF54" s="56"/>
@@ -12183,11 +12263,11 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>29.94166666666667</v>
+        <v>29.734210526315792</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12195,7 +12275,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>1.7088177461353915</v>
+        <v>1.5013616057845134</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12273,7 +12353,9 @@
       <c r="AB55" s="56">
         <v>32.1</v>
       </c>
-      <c r="AC55" s="56"/>
+      <c r="AC55" s="56">
+        <v>26.6</v>
+      </c>
       <c r="AD55" s="56"/>
       <c r="AE55" s="56"/>
       <c r="AF55" s="56"/>
@@ -12288,7 +12370,7 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12625,7 +12707,9 @@
       <c r="AB59" s="56">
         <v>29.55</v>
       </c>
-      <c r="AC59" s="99"/>
+      <c r="AC59" s="99">
+        <v>25.15</v>
+      </c>
       <c r="AD59" s="56"/>
       <c r="AE59" s="56"/>
       <c r="AF59" s="56"/>
@@ -12640,11 +12724,11 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>29.397222222222215</v>
+        <v>29.173684210526307</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12652,7 +12736,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>1.8085798388762839</v>
+        <v>1.5850418271803761</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12843,7 +12927,9 @@
       <c r="AB61" s="56">
         <v>27.15</v>
       </c>
-      <c r="AC61" s="56"/>
+      <c r="AC61" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AD61" s="56"/>
       <c r="AE61" s="56"/>
       <c r="AF61" s="56"/>
@@ -12858,11 +12944,11 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v>27.647222222222215</v>
+        <v>27.707894736842096</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12870,7 +12956,7 @@
       </c>
       <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v>1.0143224302276757</v>
+        <v>1.0749949448475569</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13215,7 +13301,9 @@
       <c r="AB65" s="56">
         <v>26.55</v>
       </c>
-      <c r="AC65" s="56"/>
+      <c r="AC65" s="56">
+        <v>26.8</v>
+      </c>
       <c r="AD65" s="56"/>
       <c r="AE65" s="56"/>
       <c r="AF65" s="56"/>
@@ -13230,11 +13318,11 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>26.206666666666667</v>
+        <v>26.243750000000002</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13242,7 +13330,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.27363360700603678</v>
+        <v>0.31071694033937192</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13318,7 +13406,9 @@
       <c r="X66" s="56">
         <v>26.95</v>
       </c>
-      <c r="Y66" s="56"/>
+      <c r="Y66" s="56">
+        <v>24.15</v>
+      </c>
       <c r="Z66" s="56">
         <v>25.9</v>
       </c>
@@ -13328,7 +13418,9 @@
       <c r="AB66" s="56">
         <v>26.8</v>
       </c>
-      <c r="AC66" s="56"/>
+      <c r="AC66" s="56">
+        <v>26.65</v>
+      </c>
       <c r="AD66" s="56"/>
       <c r="AE66" s="56"/>
       <c r="AF66" s="56"/>
@@ -13343,11 +13435,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>26.579411764705885</v>
+        <v>26.455263157894734</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13355,7 +13447,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.54606388202331502</v>
+        <v>0.42191527521216443</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13441,7 +13533,9 @@
       <c r="AB67" s="56">
         <v>25.2</v>
       </c>
-      <c r="AC67" s="56"/>
+      <c r="AC67" s="56">
+        <v>25.9</v>
+      </c>
       <c r="AD67" s="56"/>
       <c r="AE67" s="56"/>
       <c r="AF67" s="56"/>
@@ -13456,11 +13550,11 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ67" s="71">
         <f t="shared" si="1"/>
-        <v>26.613235294117651</v>
+        <v>26.573611111111113</v>
       </c>
       <c r="AR67" s="71">
         <f>IFERROR(VLOOKUP(A67,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13468,7 +13562,7 @@
       </c>
       <c r="AS67" s="71">
         <f t="shared" si="2"/>
-        <v>0.64096983617202241</v>
+        <v>0.60134565316548461</v>
       </c>
     </row>
     <row r="68" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13556,7 +13650,9 @@
       <c r="AB68" s="56">
         <v>24.25</v>
       </c>
-      <c r="AC68" s="56"/>
+      <c r="AC68" s="56">
+        <v>25.55</v>
+      </c>
       <c r="AD68" s="56"/>
       <c r="AE68" s="56"/>
       <c r="AF68" s="56"/>
@@ -13571,11 +13667,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>25.491666666666667</v>
+        <v>25.494736842105265</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13583,7 +13679,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>-0.20769356414272266</v>
+        <v>-0.20462338870412466</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13671,7 +13767,9 @@
       <c r="AB69" s="56">
         <v>24.55</v>
       </c>
-      <c r="AC69" s="56"/>
+      <c r="AC69" s="56">
+        <v>25.8</v>
+      </c>
       <c r="AD69" s="56"/>
       <c r="AE69" s="56"/>
       <c r="AF69" s="56"/>
@@ -13686,11 +13784,11 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>25.827777777777776</v>
+        <v>25.826315789473682</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13698,7 +13796,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.39392211897121499</v>
+        <v>0.39246013066712138</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13897,7 +13995,9 @@
       <c r="AB71" s="56">
         <v>27.6</v>
       </c>
-      <c r="AC71" s="56"/>
+      <c r="AC71" s="56">
+        <v>26.7</v>
+      </c>
       <c r="AD71" s="56"/>
       <c r="AE71" s="56"/>
       <c r="AF71" s="56"/>
@@ -13912,11 +14012,11 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>27.245833333333334</v>
+        <v>27.213725490196079</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13924,7 +14024,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.50189241544606489</v>
+        <v>0.46978457230881077</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14012,7 +14112,9 @@
       <c r="AB72" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="AC72" s="56"/>
+      <c r="AC72" s="56">
+        <v>25.466666666666669</v>
+      </c>
       <c r="AD72" s="56"/>
       <c r="AE72" s="56"/>
       <c r="AF72" s="56"/>
@@ -14027,11 +14129,11 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>26.05740740740741</v>
+        <v>26.026315789473689</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14039,7 +14141,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.37774130703270004</v>
+        <v>0.34664968909897809</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14232,7 +14334,9 @@
       <c r="AB74" s="56">
         <v>22.65</v>
       </c>
-      <c r="AC74" s="56"/>
+      <c r="AC74" s="56">
+        <v>21.1</v>
+      </c>
       <c r="AD74" s="56"/>
       <c r="AE74" s="56"/>
       <c r="AF74" s="56"/>
@@ -14247,11 +14351,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>22.074999999999999</v>
+        <v>22.023684210526316</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14259,7 +14363,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>1.0616121619925991</v>
+        <v>1.0102963725189156</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14347,7 +14451,9 @@
       <c r="AB75" s="56">
         <v>15.8</v>
       </c>
-      <c r="AC75" s="56"/>
+      <c r="AC75" s="56">
+        <v>15.6</v>
+      </c>
       <c r="AD75" s="56"/>
       <c r="AE75" s="56"/>
       <c r="AF75" s="56"/>
@@ -14362,11 +14468,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>16.340740740740742</v>
+        <v>16.301754385964912</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14374,7 +14480,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.63886306817493121</v>
+        <v>0.59987671339910165</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14459,8 +14565,12 @@
       <c r="AA76" s="56">
         <v>22.25</v>
       </c>
-      <c r="AB76" s="56"/>
-      <c r="AC76" s="56"/>
+      <c r="AB76" s="56">
+        <v>22.85</v>
+      </c>
+      <c r="AC76" s="56">
+        <v>20.8</v>
+      </c>
       <c r="AD76" s="56"/>
       <c r="AE76" s="56"/>
       <c r="AF76" s="56"/>
@@ -14475,11 +14585,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>21.435294117647061</v>
+        <v>21.476315789473688</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14487,7 +14597,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>1.1060112272190601</v>
+        <v>1.1470328990456871</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14575,7 +14685,9 @@
       <c r="AB77" s="56">
         <v>26</v>
       </c>
-      <c r="AC77" s="56"/>
+      <c r="AC77" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AD77" s="56"/>
       <c r="AE77" s="56"/>
       <c r="AF77" s="56"/>
@@ -14590,11 +14702,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>25.040740740740745</v>
+        <v>25.070175438596497</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14602,7 +14714,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.8595504520802137</v>
+        <v>1.8889851499359658</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14688,7 +14800,9 @@
       <c r="AB78" s="56">
         <v>34.6</v>
       </c>
-      <c r="AC78" s="56"/>
+      <c r="AC78" s="56">
+        <v>32.25</v>
+      </c>
       <c r="AD78" s="56"/>
       <c r="AE78" s="56"/>
       <c r="AF78" s="56"/>
@@ -14703,11 +14817,11 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v>33.141176470588235</v>
+        <v>33.091666666666669</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14715,7 +14829,7 @@
       </c>
       <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v>3.168597898198044</v>
+        <v>3.1190880942764778</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14803,7 +14917,9 @@
       <c r="AB79" s="56">
         <v>33.06666666666667</v>
       </c>
-      <c r="AC79" s="56"/>
+      <c r="AC79" s="56">
+        <v>31.6</v>
+      </c>
       <c r="AD79" s="56"/>
       <c r="AE79" s="56"/>
       <c r="AF79" s="56"/>
@@ -14818,11 +14934,11 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ79" s="71">
         <f t="shared" si="4"/>
-        <v>32.912962962962965</v>
+        <v>32.843859649122813</v>
       </c>
       <c r="AR79" s="71">
         <f>IFERROR(VLOOKUP(A79,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14830,7 +14946,7 @@
       </c>
       <c r="AS79" s="71">
         <f t="shared" si="5"/>
-        <v>2.7811379614775333</v>
+        <v>2.7120346476373811</v>
       </c>
     </row>
     <row r="80" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14915,8 +15031,12 @@
       <c r="AA80" s="56">
         <v>21.6</v>
       </c>
-      <c r="AB80" s="56"/>
-      <c r="AC80" s="56"/>
+      <c r="AB80" s="56">
+        <v>22.4</v>
+      </c>
+      <c r="AC80" s="56">
+        <v>22.06666666666667</v>
+      </c>
       <c r="AD80" s="56"/>
       <c r="AE80" s="56"/>
       <c r="AF80" s="56"/>
@@ -14931,11 +15051,11 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ80" s="71">
         <f t="shared" si="4"/>
-        <v>21.803921568627455</v>
+        <v>21.849122807017547</v>
       </c>
       <c r="AR80" s="71">
         <f>IFERROR(VLOOKUP(A80,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14943,7 +15063,7 @@
       </c>
       <c r="AS80" s="71">
         <f t="shared" si="5"/>
-        <v>1.4036552227189958</v>
+        <v>1.4488564611090879</v>
       </c>
     </row>
     <row r="81" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15146,7 +15266,9 @@
       <c r="AB82" s="56">
         <v>27.4</v>
       </c>
-      <c r="AC82" s="56"/>
+      <c r="AC82" s="56">
+        <v>27.93333333333333</v>
+      </c>
       <c r="AD82" s="56"/>
       <c r="AE82" s="56"/>
       <c r="AF82" s="56"/>
@@ -15161,11 +15283,11 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>27.346296296296295</v>
+        <v>27.377192982456137</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15173,7 +15295,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>0.92386634890229402</v>
+        <v>0.95476303506213611</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15412,8 +15534,12 @@
       <c r="AA85" s="56">
         <v>32.549999999999997</v>
       </c>
-      <c r="AB85" s="56"/>
-      <c r="AC85" s="56"/>
+      <c r="AB85" s="56">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="AC85" s="56">
+        <v>31.65</v>
+      </c>
       <c r="AD85" s="56"/>
       <c r="AE85" s="56"/>
       <c r="AF85" s="56"/>
@@ -15428,11 +15554,11 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v>31.798888888888886</v>
+        <v>31.872549019607838</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15526,7 +15652,9 @@
         <v>32.099999999999987</v>
       </c>
       <c r="AB86" s="56"/>
-      <c r="AC86" s="56"/>
+      <c r="AC86" s="56">
+        <v>31.45</v>
+      </c>
       <c r="AD86" s="56"/>
       <c r="AE86" s="56"/>
       <c r="AF86" s="56"/>
@@ -15541,11 +15669,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>30.408823529411766</v>
+        <v>30.466666666666672</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15553,7 +15681,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>2.1423294369651451</v>
+        <v>2.2001725742200513</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15635,9 +15763,13 @@
       <c r="Z87" s="56">
         <v>28.2</v>
       </c>
-      <c r="AA87" s="56"/>
+      <c r="AA87" s="56">
+        <v>32.35</v>
+      </c>
       <c r="AB87" s="56"/>
-      <c r="AC87" s="56"/>
+      <c r="AC87" s="56">
+        <v>27.9</v>
+      </c>
       <c r="AD87" s="56"/>
       <c r="AE87" s="56"/>
       <c r="AF87" s="56"/>
@@ -15652,11 +15784,11 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ87" s="71">
         <f t="shared" si="4"/>
-        <v>30.593750000000004</v>
+        <v>30.541666666666668</v>
       </c>
       <c r="AR87" s="71">
         <f>IFERROR(VLOOKUP(A87,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15664,7 +15796,7 @@
       </c>
       <c r="AS87" s="71">
         <f t="shared" si="5"/>
-        <v>2.1262745859213332</v>
+        <v>2.0741912525879975</v>
       </c>
     </row>
     <row r="88" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15752,7 +15884,9 @@
       <c r="AB88" s="56">
         <v>31.35</v>
       </c>
-      <c r="AC88" s="56"/>
+      <c r="AC88" s="56">
+        <v>27.55</v>
+      </c>
       <c r="AD88" s="56"/>
       <c r="AE88" s="56"/>
       <c r="AF88" s="56"/>
@@ -15767,11 +15901,11 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>30.286111111111115</v>
+        <v>30.142105263157898</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15779,7 +15913,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>2.7989847836366444</v>
+        <v>2.6549789356834275</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15861,7 +15995,9 @@
       <c r="AB89" s="56">
         <v>32.849999999999987</v>
       </c>
-      <c r="AC89" s="56"/>
+      <c r="AC89" s="56">
+        <v>26.8</v>
+      </c>
       <c r="AD89" s="56"/>
       <c r="AE89" s="56"/>
       <c r="AF89" s="56"/>
@@ -15876,11 +16012,11 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>31.313333333333329</v>
+        <v>31.031249999999996</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15888,7 +16024,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>3.1563195926075487</v>
+        <v>2.8742362592742161</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15973,7 +16109,9 @@
       <c r="AA90" s="56">
         <v>33.700000000000003</v>
       </c>
-      <c r="AB90" s="56"/>
+      <c r="AB90" s="56">
+        <v>34.200000000000003</v>
+      </c>
       <c r="AC90" s="56"/>
       <c r="AD90" s="56"/>
       <c r="AE90" s="56"/>
@@ -15989,11 +16127,11 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ90" s="71">
         <f t="shared" si="4"/>
-        <v>31.914705882352937</v>
+        <v>32.041666666666664</v>
       </c>
       <c r="AR90" s="71">
         <f>IFERROR(VLOOKUP(A90,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16001,7 +16139,7 @@
       </c>
       <c r="AS90" s="71">
         <f t="shared" si="5"/>
-        <v>4.2289664802286069</v>
+        <v>4.3559272645423341</v>
       </c>
     </row>
     <row r="91" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16089,7 +16227,9 @@
       <c r="AB91" s="56">
         <v>30.375</v>
       </c>
-      <c r="AC91" s="56"/>
+      <c r="AC91" s="56">
+        <v>31.1</v>
+      </c>
       <c r="AD91" s="56"/>
       <c r="AE91" s="56"/>
       <c r="AF91" s="56"/>
@@ -16104,11 +16244,11 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ91" s="71">
         <f t="shared" si="4"/>
-        <v>31.019444444444446</v>
+        <v>31.023684210526319</v>
       </c>
       <c r="AR91" s="71" t="str">
         <f>IFERROR(VLOOKUP(A91,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16204,7 +16344,9 @@
       <c r="AB92" s="56">
         <v>19.7</v>
       </c>
-      <c r="AC92" s="56"/>
+      <c r="AC92" s="56">
+        <v>18.149999999999999</v>
+      </c>
       <c r="AD92" s="56"/>
       <c r="AE92" s="56"/>
       <c r="AF92" s="56"/>
@@ -16219,11 +16361,11 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ92" s="71">
         <f t="shared" si="4"/>
-        <v>18.516666666666666</v>
+        <v>18.497368421052631</v>
       </c>
       <c r="AR92" s="71">
         <f>IFERROR(VLOOKUP(A92,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16231,7 +16373,7 @@
       </c>
       <c r="AS92" s="71">
         <f t="shared" si="5"/>
-        <v>2.2785291005291342</v>
+        <v>2.2592308549150992</v>
       </c>
     </row>
     <row r="93" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16319,7 +16461,9 @@
       <c r="AB93" s="56">
         <v>26.6</v>
       </c>
-      <c r="AC93" s="56"/>
+      <c r="AC93" s="56">
+        <v>25</v>
+      </c>
       <c r="AD93" s="56"/>
       <c r="AE93" s="56"/>
       <c r="AF93" s="56"/>
@@ -16334,11 +16478,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>25.337037037037035</v>
+        <v>25.319298245614036</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16346,7 +16490,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>3.0539143589743851</v>
+        <v>3.0361755675513855</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16426,9 +16570,11 @@
         <v>17.7</v>
       </c>
       <c r="AB94" s="56">
-        <v>17.93333333333333</v>
-      </c>
-      <c r="AC94" s="56"/>
+        <v>17.5</v>
+      </c>
+      <c r="AC94" s="56">
+        <v>18.350000000000001</v>
+      </c>
       <c r="AD94" s="56"/>
       <c r="AE94" s="56"/>
       <c r="AF94" s="56"/>
@@ -16443,11 +16589,11 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.855555555555554</v>
+        <v>17.859375</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16455,7 +16601,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.5593730269462647</v>
+        <v>1.5631924713907104</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16543,7 +16689,9 @@
       <c r="AB95" s="56">
         <v>14.3</v>
       </c>
-      <c r="AC95" s="56"/>
+      <c r="AC95" s="56">
+        <v>14.7</v>
+      </c>
       <c r="AD95" s="56"/>
       <c r="AE95" s="56"/>
       <c r="AF95" s="56"/>
@@ -16558,11 +16706,11 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>14.697222222222219</v>
+        <v>14.697368421052628</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16570,7 +16718,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>0.81149608350119884</v>
+        <v>0.81164228233160784</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16735,7 +16883,9 @@
       <c r="AB97" s="56">
         <v>15.53333333333333</v>
       </c>
-      <c r="AC97" s="56"/>
+      <c r="AC97" s="56">
+        <v>15</v>
+      </c>
       <c r="AD97" s="56"/>
       <c r="AE97" s="56"/>
       <c r="AF97" s="56"/>
@@ -16750,11 +16900,11 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ97" s="71">
         <f t="shared" si="4"/>
-        <v>16.617647058823522</v>
+        <v>16.527777777777771</v>
       </c>
       <c r="AR97" s="71">
         <f>IFERROR(VLOOKUP(A97,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16762,7 +16912,7 @@
       </c>
       <c r="AS97" s="71">
         <f t="shared" si="5"/>
-        <v>2.2986019278290524</v>
+        <v>2.2087326467833019</v>
       </c>
     </row>
     <row r="98" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16850,7 +17000,9 @@
       <c r="AB98" s="56">
         <v>13.8</v>
       </c>
-      <c r="AC98" s="56"/>
+      <c r="AC98" s="56">
+        <v>12.3</v>
+      </c>
       <c r="AD98" s="56"/>
       <c r="AE98" s="56"/>
       <c r="AF98" s="56"/>
@@ -16865,11 +17017,11 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>13.088888888888889</v>
+        <v>13.047368421052632</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16963,7 +17115,9 @@
       <c r="AB99" s="56">
         <v>16.533333333333331</v>
       </c>
-      <c r="AC99" s="56"/>
+      <c r="AC99" s="56">
+        <v>14.93333333333333</v>
+      </c>
       <c r="AD99" s="56"/>
       <c r="AE99" s="56"/>
       <c r="AF99" s="56"/>
@@ -16978,11 +17132,11 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>15.34313725490196</v>
+        <v>15.32037037037037</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17078,7 +17232,9 @@
       <c r="AB100" s="56">
         <v>16.2</v>
       </c>
-      <c r="AC100" s="56"/>
+      <c r="AC100" s="56">
+        <v>15.866666666666671</v>
+      </c>
       <c r="AD100" s="56"/>
       <c r="AE100" s="56"/>
       <c r="AF100" s="56"/>
@@ -17093,11 +17249,11 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ100" s="71">
         <f t="shared" si="4"/>
-        <v>16.162962962962961</v>
+        <v>16.147368421052629</v>
       </c>
       <c r="AR100" s="71">
         <f>IFERROR(VLOOKUP(A100,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17105,7 +17261,7 @@
       </c>
       <c r="AS100" s="71">
         <f t="shared" si="5"/>
-        <v>1.6796473686557718</v>
+        <v>1.66405282674544</v>
       </c>
     </row>
     <row r="101" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17193,7 +17349,9 @@
       <c r="AB101" s="56">
         <v>14.05</v>
       </c>
-      <c r="AC101" s="56"/>
+      <c r="AC101" s="56">
+        <v>13.5</v>
+      </c>
       <c r="AD101" s="56"/>
       <c r="AE101" s="56"/>
       <c r="AF101" s="56"/>
@@ -17208,11 +17366,11 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>13.680555555555555</v>
+        <v>13.671052631578947</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17220,7 +17378,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>0.86141021862508538</v>
+        <v>0.85190729464847692</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17293,7 +17451,9 @@
       <c r="AA102" s="56">
         <v>13.53333333333333</v>
       </c>
-      <c r="AB102" s="56"/>
+      <c r="AB102" s="56">
+        <v>13.06666666666667</v>
+      </c>
       <c r="AC102" s="56"/>
       <c r="AD102" s="56"/>
       <c r="AE102" s="56"/>
@@ -17309,7 +17469,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17567,7 +17727,9 @@
       <c r="AB105" s="56">
         <v>20.8</v>
       </c>
-      <c r="AC105" s="56"/>
+      <c r="AC105" s="56">
+        <v>19.333333333333329</v>
+      </c>
       <c r="AD105" s="56"/>
       <c r="AE105" s="56"/>
       <c r="AF105" s="56"/>
@@ -17582,11 +17744,11 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>19.825925925925926</v>
+        <v>19.8</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17594,7 +17756,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>2.514409563173416</v>
+        <v>2.4884836372474908</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17654,7 +17816,9 @@
       <c r="AB106" s="56">
         <v>14.1</v>
       </c>
-      <c r="AC106" s="56"/>
+      <c r="AC106" s="56">
+        <v>14.8</v>
+      </c>
       <c r="AD106" s="56"/>
       <c r="AE106" s="56"/>
       <c r="AF106" s="56"/>
@@ -17669,7 +17833,7 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ106" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17852,7 +18016,9 @@
       <c r="AB108" s="56">
         <v>12.4</v>
       </c>
-      <c r="AC108" s="56"/>
+      <c r="AC108" s="56">
+        <v>14.25</v>
+      </c>
       <c r="AD108" s="56"/>
       <c r="AE108" s="56"/>
       <c r="AF108" s="56"/>
@@ -17867,11 +18033,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>13.691666666666666</v>
+        <v>13.721052631578948</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17879,7 +18045,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>-0.63660197102407423</v>
+        <v>-0.60721600611179305</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17967,7 +18133,9 @@
       <c r="AB109" s="56">
         <v>15.25</v>
       </c>
-      <c r="AC109" s="56"/>
+      <c r="AC109" s="56">
+        <v>13.35</v>
+      </c>
       <c r="AD109" s="56"/>
       <c r="AE109" s="56"/>
       <c r="AF109" s="56"/>
@@ -17982,11 +18150,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>14.763888888888889</v>
+        <v>14.689473684210528</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17994,7 +18162,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>0.67938001277140003</v>
+        <v>0.60496480809303854</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18076,7 +18244,9 @@
       <c r="AB110" s="56">
         <v>17.466666666666669</v>
       </c>
-      <c r="AC110" s="56"/>
+      <c r="AC110" s="56">
+        <v>17.13333333333334</v>
+      </c>
       <c r="AD110" s="56"/>
       <c r="AE110" s="56"/>
       <c r="AF110" s="56"/>
@@ -18091,11 +18261,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>17.915555555555557</v>
+        <v>17.866666666666667</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18103,7 +18273,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.25979559976079614</v>
+        <v>0.21090671087190671</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18191,7 +18361,9 @@
       <c r="AB111" s="56">
         <v>15.733333333333331</v>
       </c>
-      <c r="AC111" s="56"/>
+      <c r="AC111" s="56">
+        <v>15.733333333333331</v>
+      </c>
       <c r="AD111" s="56"/>
       <c r="AE111" s="56"/>
       <c r="AF111" s="56"/>
@@ -18206,11 +18378,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>15.91111111111111</v>
+        <v>15.901754385964912</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18218,7 +18390,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.10797740972310876</v>
+        <v>9.8620684576911088E-2</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18306,7 +18478,9 @@
       <c r="AB112" s="56">
         <v>18</v>
       </c>
-      <c r="AC112" s="56"/>
+      <c r="AC112" s="56">
+        <v>18.666666666666671</v>
+      </c>
       <c r="AD112" s="56"/>
       <c r="AE112" s="56"/>
       <c r="AF112" s="56"/>
@@ -18321,11 +18495,11 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>18.607407407407404</v>
+        <v>18.610526315789471</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18333,7 +18507,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.3707799005925132</v>
+        <v>1.3738988089745803</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18516,7 +18690,9 @@
       <c r="AB114" s="56">
         <v>21.8</v>
       </c>
-      <c r="AC114" s="56"/>
+      <c r="AC114" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="AD114" s="56"/>
       <c r="AE114" s="56"/>
       <c r="AF114" s="56"/>
@@ -18531,7 +18707,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18631,7 +18807,9 @@
       <c r="AB115" s="56">
         <v>27.25</v>
       </c>
-      <c r="AC115" s="56"/>
+      <c r="AC115" s="56">
+        <v>27</v>
+      </c>
       <c r="AD115" s="56"/>
       <c r="AE115" s="56"/>
       <c r="AF115" s="56"/>
@@ -18646,11 +18824,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>27.644444444444446</v>
+        <v>27.610526315789475</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18658,7 +18836,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.20898516553692659</v>
+        <v>0.17506703688195557</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18746,7 +18924,9 @@
       <c r="AB116" s="56">
         <v>19.266666666666669</v>
       </c>
-      <c r="AC116" s="56"/>
+      <c r="AC116" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="AD116" s="56"/>
       <c r="AE116" s="56"/>
       <c r="AF116" s="56"/>
@@ -18761,11 +18941,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.546296296296294</v>
+        <v>19.556140350877193</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18773,7 +18953,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.54791642097824322</v>
+        <v>0.55776047555914232</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18859,7 +19039,9 @@
       <c r="AB117" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="AC117" s="56"/>
+      <c r="AC117" s="56">
+        <v>27</v>
+      </c>
       <c r="AD117" s="56"/>
       <c r="AE117" s="56"/>
       <c r="AF117" s="56"/>
@@ -18874,11 +19056,11 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v>27.121568627450987</v>
+        <v>27.114814814814821</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18886,7 +19068,7 @@
       </c>
       <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v>0.72957864808172701</v>
+        <v>0.72282483544556086</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18964,7 +19146,9 @@
       <c r="AB118" s="56">
         <v>30.8</v>
       </c>
-      <c r="AC118" s="56"/>
+      <c r="AC118" s="56">
+        <v>28.06666666666667</v>
+      </c>
       <c r="AD118" s="56"/>
       <c r="AE118" s="56"/>
       <c r="AF118" s="56"/>
@@ -18979,7 +19163,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19362,7 +19546,9 @@
       <c r="AB122" s="56">
         <v>12.733333333333331</v>
       </c>
-      <c r="AC122" s="56"/>
+      <c r="AC122" s="56">
+        <v>12.4</v>
+      </c>
       <c r="AD122" s="56"/>
       <c r="AE122" s="56"/>
       <c r="AF122" s="56"/>
@@ -19377,11 +19563,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.907407407407405</v>
+        <v>12.880701754385962</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19389,7 +19575,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>2.4267942518961654</v>
+        <v>2.4000885988747225</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19744,7 +19930,9 @@
       <c r="AB126" s="56">
         <v>11.8</v>
       </c>
-      <c r="AC126" s="56"/>
+      <c r="AC126" s="56">
+        <v>12.133333333333329</v>
+      </c>
       <c r="AD126" s="56"/>
       <c r="AE126" s="56"/>
       <c r="AF126" s="56"/>
@@ -19759,11 +19947,11 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ126" s="71">
         <f t="shared" si="4"/>
-        <v>11.984444444444444</v>
+        <v>11.993749999999999</v>
       </c>
       <c r="AR126" s="71">
         <f>IFERROR(VLOOKUP(A126,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19771,7 +19959,7 @@
       </c>
       <c r="AS126" s="71">
         <f t="shared" si="5"/>
-        <v>0.9130812316642043</v>
+        <v>0.92238678721975909</v>
       </c>
     </row>
     <row r="127" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20096,7 +20284,9 @@
       <c r="AB130" s="56">
         <v>16.3</v>
       </c>
-      <c r="AC130" s="56"/>
+      <c r="AC130" s="56">
+        <v>17.06666666666667</v>
+      </c>
       <c r="AD130" s="56"/>
       <c r="AE130" s="56"/>
       <c r="AF130" s="56"/>
@@ -20111,11 +20301,11 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>16.194444444444443</v>
+        <v>16.240350877192981</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20123,7 +20313,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.784681880762923</v>
+        <v>1.8305883135114609</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20211,7 +20401,9 @@
       <c r="AB131" s="56">
         <v>18.5</v>
       </c>
-      <c r="AC131" s="56"/>
+      <c r="AC131" s="56">
+        <v>18.5</v>
+      </c>
       <c r="AD131" s="56"/>
       <c r="AE131" s="56"/>
       <c r="AF131" s="56"/>
@@ -20226,11 +20418,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>18.811111111111114</v>
+        <v>18.794736842105266</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20238,7 +20430,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>1.6508336030397643</v>
+        <v>1.6344593340339166</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20405,7 +20597,9 @@
       <c r="AB133" s="56">
         <v>14</v>
       </c>
-      <c r="AC133" s="56"/>
+      <c r="AC133" s="56">
+        <v>14.46666666666667</v>
+      </c>
       <c r="AD133" s="56"/>
       <c r="AE133" s="56"/>
       <c r="AF133" s="56"/>
@@ -20420,11 +20614,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>14.007407407407406</v>
+        <v>14.03157894736842</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20432,7 +20626,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>0.93782319306386697</v>
+        <v>0.96199473302488059</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20520,7 +20714,9 @@
       <c r="AB134" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="AC134" s="56"/>
+      <c r="AC134" s="56">
+        <v>18.533333333333331</v>
+      </c>
       <c r="AD134" s="56"/>
       <c r="AE134" s="56"/>
       <c r="AF134" s="56"/>
@@ -20535,11 +20731,11 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>18.42962962962963</v>
+        <v>18.435087719298245</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20547,7 +20743,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>2.2763935249510112</v>
+        <v>2.2818516146196259</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20635,7 +20831,9 @@
       <c r="AB135" s="56">
         <v>22.7</v>
       </c>
-      <c r="AC135" s="56"/>
+      <c r="AC135" s="56">
+        <v>21.65</v>
+      </c>
       <c r="AD135" s="56"/>
       <c r="AE135" s="56"/>
       <c r="AF135" s="56"/>
@@ -20650,11 +20848,11 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>21.697222222222219</v>
+        <v>21.694736842105261</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20662,7 +20860,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>3.1891763997251488</v>
+        <v>3.1866910196081903</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20745,8 +20943,12 @@
       <c r="AA136" s="56">
         <v>11.733333333333331</v>
       </c>
-      <c r="AB136" s="56"/>
-      <c r="AC136" s="56"/>
+      <c r="AB136" s="56">
+        <v>11.33333333333333</v>
+      </c>
+      <c r="AC136" s="56">
+        <v>10.06666666666667</v>
+      </c>
       <c r="AD136" s="56"/>
       <c r="AE136" s="56"/>
       <c r="AF136" s="56"/>
@@ -20761,11 +20963,11 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ136" s="71">
         <f t="shared" si="7"/>
-        <v>11.395833333333332</v>
+        <v>11.318518518518518</v>
       </c>
       <c r="AR136" s="71">
         <f>IFERROR(VLOOKUP(A136,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20773,7 +20975,7 @@
       </c>
       <c r="AS136" s="71">
         <f t="shared" si="8"/>
-        <v>4.5765151515162472E-2</v>
+        <v>-3.1549663299651698E-2</v>
       </c>
     </row>
     <row r="137" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20940,7 +21142,9 @@
       <c r="AB138" s="56">
         <v>23.333333333333329</v>
       </c>
-      <c r="AC138" s="56"/>
+      <c r="AC138" s="56">
+        <v>22.4</v>
+      </c>
       <c r="AD138" s="56"/>
       <c r="AE138" s="56"/>
       <c r="AF138" s="56"/>
@@ -20955,11 +21159,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>23.140740740740736</v>
+        <v>23.101754385964906</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20967,7 +21171,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>2.9281913762778942</v>
+        <v>2.8892050215020646</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21049,7 +21253,9 @@
       <c r="AB139" s="56">
         <v>14.225</v>
       </c>
-      <c r="AC139" s="56"/>
+      <c r="AC139" s="56">
+        <v>14.775</v>
+      </c>
       <c r="AD139" s="56"/>
       <c r="AE139" s="56"/>
       <c r="AF139" s="56"/>
@@ -21064,11 +21270,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.261666666666663</v>
+        <v>14.293749999999998</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21076,7 +21282,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.0169289480774033</v>
+        <v>1.0490122814107377</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21164,7 +21370,9 @@
       <c r="AB140" s="56">
         <v>16.399999999999999</v>
       </c>
-      <c r="AC140" s="56"/>
+      <c r="AC140" s="56">
+        <v>16.2</v>
+      </c>
       <c r="AD140" s="56"/>
       <c r="AE140" s="56"/>
       <c r="AF140" s="56"/>
@@ -21179,11 +21387,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.399999999999999</v>
+        <v>16.389473684210525</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21191,7 +21399,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.53199603174603816</v>
+        <v>0.52146971595656488</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21279,7 +21487,9 @@
       <c r="AB141" s="56">
         <v>13.46666666666667</v>
       </c>
-      <c r="AC141" s="56"/>
+      <c r="AC141" s="56">
+        <v>13.66666666666667</v>
+      </c>
       <c r="AD141" s="56"/>
       <c r="AE141" s="56"/>
       <c r="AF141" s="56"/>
@@ -21294,11 +21504,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>13.566666666666668</v>
+        <v>13.571929824561403</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21306,7 +21516,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.1511083066408183</v>
+        <v>1.1563714645355532</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21394,7 +21604,9 @@
       <c r="AB142" s="56">
         <v>11.4</v>
       </c>
-      <c r="AC142" s="56"/>
+      <c r="AC142" s="56">
+        <v>11.35</v>
+      </c>
       <c r="AD142" s="56"/>
       <c r="AE142" s="56"/>
       <c r="AF142" s="56"/>
@@ -21409,11 +21621,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>11.529166666666665</v>
+        <v>11.519736842105262</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21421,7 +21633,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>0.65033065404393575</v>
+        <v>0.64090082948253269</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21509,7 +21721,9 @@
       <c r="AB143" s="56">
         <v>28.4</v>
       </c>
-      <c r="AC143" s="56"/>
+      <c r="AC143" s="56">
+        <v>26.466666666666669</v>
+      </c>
       <c r="AD143" s="56"/>
       <c r="AE143" s="56"/>
       <c r="AF143" s="56"/>
@@ -21524,11 +21738,11 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ143" s="71">
         <f t="shared" si="7"/>
-        <v>27.896296296296295</v>
+        <v>27.821052631578947</v>
       </c>
       <c r="AR143" s="71">
         <f>IFERROR(VLOOKUP(A143,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21536,7 +21750,7 @@
       </c>
       <c r="AS143" s="71">
         <f t="shared" si="8"/>
-        <v>2.0511691411238964</v>
+        <v>1.9759254764065481</v>
       </c>
     </row>
     <row r="144" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21735,7 +21949,9 @@
       <c r="AB145" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="AC145" s="56"/>
+      <c r="AC145" s="56">
+        <v>20.8</v>
+      </c>
       <c r="AD145" s="56"/>
       <c r="AE145" s="56"/>
       <c r="AF145" s="56"/>
@@ -21750,11 +21966,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>20.69259259259259</v>
+        <v>20.698245614035088</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21762,7 +21978,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>1.0831695767766796</v>
+        <v>1.0888225982191777</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21847,8 +22063,12 @@
       <c r="AA146" s="56">
         <v>31.6</v>
       </c>
-      <c r="AB146" s="56"/>
-      <c r="AC146" s="56"/>
+      <c r="AB146" s="56">
+        <v>33.266666666666673</v>
+      </c>
+      <c r="AC146" s="56">
+        <v>31.6</v>
+      </c>
       <c r="AD146" s="56"/>
       <c r="AE146" s="56"/>
       <c r="AF146" s="56"/>
@@ -21863,11 +22083,11 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v>31.103921568627449</v>
+        <v>31.243859649122808</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21875,7 +22095,7 @@
       </c>
       <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v>1.7461710260005781</v>
+        <v>1.8861091064959368</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21963,7 +22183,9 @@
       <c r="AB147" s="56">
         <v>28</v>
       </c>
-      <c r="AC147" s="56"/>
+      <c r="AC147" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AD147" s="56"/>
       <c r="AE147" s="56"/>
       <c r="AF147" s="56"/>
@@ -21978,11 +22200,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>26.640740740740743</v>
+        <v>26.628070175438598</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21990,7 +22212,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>2.5155283750248323</v>
+        <v>2.5028578097226877</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22075,8 +22297,12 @@
       <c r="AA148" s="56">
         <v>31.4</v>
       </c>
-      <c r="AB148" s="56"/>
-      <c r="AC148" s="56"/>
+      <c r="AB148" s="56">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="AC148" s="56">
+        <v>33.533333333333331</v>
+      </c>
       <c r="AD148" s="56"/>
       <c r="AE148" s="56"/>
       <c r="AF148" s="56"/>
@@ -22091,11 +22317,11 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>30.580392156862747</v>
+        <v>30.957894736842103</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22103,7 +22329,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.6514127997182975</v>
+        <v>2.0289153796976542</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22191,7 +22417,9 @@
       <c r="AB149" s="56">
         <v>24.06666666666667</v>
       </c>
-      <c r="AC149" s="56"/>
+      <c r="AC149" s="56">
+        <v>23.266666666666669</v>
+      </c>
       <c r="AD149" s="56"/>
       <c r="AE149" s="56"/>
       <c r="AF149" s="56"/>
@@ -22206,11 +22434,11 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ149" s="71">
         <f t="shared" si="7"/>
-        <v>23.850000000000005</v>
+        <v>23.819298245614039</v>
       </c>
       <c r="AR149" s="71">
         <f>IFERROR(VLOOKUP(A149,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22218,7 +22446,7 @@
       </c>
       <c r="AS149" s="71">
         <f t="shared" si="8"/>
-        <v>2.3468584656084737</v>
+        <v>2.3161567112225079</v>
       </c>
     </row>
     <row r="150" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22644,7 +22872,9 @@
       <c r="AB154" s="56">
         <v>22.75</v>
       </c>
-      <c r="AC154" s="56"/>
+      <c r="AC154" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AD154" s="56"/>
       <c r="AE154" s="56"/>
       <c r="AF154" s="56"/>
@@ -22659,7 +22889,7 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ154" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22759,7 +22989,9 @@
       <c r="AB155" s="56">
         <v>28.466666666666669</v>
       </c>
-      <c r="AC155" s="56"/>
+      <c r="AC155" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="AD155" s="56"/>
       <c r="AE155" s="56"/>
       <c r="AF155" s="56"/>
@@ -22774,11 +23006,11 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>29.107407407407404</v>
+        <v>28.989473684210523</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22786,7 +23018,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>1.4559470963150254</v>
+        <v>1.3380133731181445</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23060,7 +23292,9 @@
       <c r="AB158" s="56">
         <v>32.200000000000003</v>
       </c>
-      <c r="AC158" s="56"/>
+      <c r="AC158" s="56">
+        <v>28.13333333333334</v>
+      </c>
       <c r="AD158" s="56"/>
       <c r="AE158" s="56"/>
       <c r="AF158" s="56"/>
@@ -23075,11 +23309,11 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ158" s="71">
         <f t="shared" si="7"/>
-        <v>31.055555555555557</v>
+        <v>30.90175438596491</v>
       </c>
       <c r="AR158" s="71">
         <f>IFERROR(VLOOKUP(A158,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23087,7 +23321,7 @@
       </c>
       <c r="AS158" s="71">
         <f t="shared" si="8"/>
-        <v>3.3294649921254482</v>
+        <v>3.1756638225348013</v>
       </c>
     </row>
     <row r="159" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23175,7 +23409,9 @@
       <c r="AB159" s="56">
         <v>22.466666666666669</v>
       </c>
-      <c r="AC159" s="56"/>
+      <c r="AC159" s="56">
+        <v>21.133333333333329</v>
+      </c>
       <c r="AD159" s="56"/>
       <c r="AE159" s="56"/>
       <c r="AF159" s="56"/>
@@ -23190,11 +23426,11 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>21.325925925925926</v>
+        <v>21.315789473684209</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23202,7 +23438,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>2.4908675629540653</v>
+        <v>2.4807311107123482</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23288,7 +23524,9 @@
       <c r="AB160" s="56">
         <v>27.266666666666669</v>
       </c>
-      <c r="AC160" s="56"/>
+      <c r="AC160" s="56">
+        <v>27.333333333333329</v>
+      </c>
       <c r="AD160" s="56"/>
       <c r="AE160" s="56"/>
       <c r="AF160" s="56"/>
@@ -23303,11 +23541,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.494117647058822</v>
+        <v>27.485185185185184</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23597,7 +23835,9 @@
       <c r="AB163" s="56">
         <v>23</v>
       </c>
-      <c r="AC163" s="56"/>
+      <c r="AC163" s="56">
+        <v>20.6</v>
+      </c>
       <c r="AD163" s="56"/>
       <c r="AE163" s="56"/>
       <c r="AF163" s="56"/>
@@ -23612,11 +23852,11 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.659259259259258</v>
+        <v>21.603508771929825</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23624,7 +23864,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.43029868785253811</v>
+        <v>0.37454820052310467</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23712,7 +23952,9 @@
       <c r="AB164" s="56">
         <v>26.1</v>
       </c>
-      <c r="AC164" s="56"/>
+      <c r="AC164" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AD164" s="56"/>
       <c r="AE164" s="56"/>
       <c r="AF164" s="56"/>
@@ -23727,11 +23969,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.677777777777777</v>
+        <v>25.652631578947368</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23739,7 +23981,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.7862197728516875</v>
+        <v>1.7610735740212782</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23906,7 +24148,9 @@
       <c r="AB166" s="56">
         <v>15.4</v>
       </c>
-      <c r="AC166" s="56"/>
+      <c r="AC166" s="56">
+        <v>14.8</v>
+      </c>
       <c r="AD166" s="56"/>
       <c r="AE166" s="56"/>
       <c r="AF166" s="56"/>
@@ -23921,11 +24165,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.864814814814814</v>
+        <v>14.861403508771931</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23933,7 +24177,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.2441481481481844</v>
+        <v>1.2407368421053011</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24021,7 +24265,9 @@
       <c r="AB167" s="56">
         <v>21.8</v>
       </c>
-      <c r="AC167" s="56"/>
+      <c r="AC167" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AD167" s="56"/>
       <c r="AE167" s="56"/>
       <c r="AF167" s="56"/>
@@ -24036,11 +24282,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>21.433333333333337</v>
+        <v>21.414035087719302</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24048,7 +24294,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>2.3512446462683272</v>
+        <v>2.3319464006542923</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24136,7 +24382,9 @@
       <c r="AB168" s="56">
         <v>30.25</v>
       </c>
-      <c r="AC168" s="56"/>
+      <c r="AC168" s="56">
+        <v>27</v>
+      </c>
       <c r="AD168" s="56"/>
       <c r="AE168" s="56"/>
       <c r="AF168" s="56"/>
@@ -24151,11 +24399,11 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>28.705555555555559</v>
+        <v>28.615789473684213</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24163,7 +24411,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>2.6085701693172787</v>
+        <v>2.5188040874459325</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24251,7 +24499,9 @@
       <c r="AB169" s="56">
         <v>9.1499999999999986</v>
       </c>
-      <c r="AC169" s="56"/>
+      <c r="AC169" s="56">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="AD169" s="56"/>
       <c r="AE169" s="56"/>
       <c r="AF169" s="56"/>
@@ -24266,11 +24516,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>9.43611111111111</v>
+        <v>9.4499999999999975</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24278,7 +24528,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>0.31474128494045495</v>
+        <v>0.32863017382934245</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24441,7 +24691,9 @@
       </c>
       <c r="O171" s="56"/>
       <c r="P171" s="56"/>
-      <c r="Q171" s="56"/>
+      <c r="Q171" s="56">
+        <v>21.4</v>
+      </c>
       <c r="R171" s="56">
         <v>22.86666666666666</v>
       </c>
@@ -24475,7 +24727,9 @@
       <c r="AB171" s="56">
         <v>22.2</v>
       </c>
-      <c r="AC171" s="56"/>
+      <c r="AC171" s="56">
+        <v>23.333333333333329</v>
+      </c>
       <c r="AD171" s="56"/>
       <c r="AE171" s="56"/>
       <c r="AF171" s="56"/>
@@ -24490,11 +24744,11 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ171" s="71">
         <f t="shared" si="7"/>
-        <v>22.328888888888891</v>
+        <v>22.333333333333332</v>
       </c>
       <c r="AR171" s="71">
         <f>IFERROR(VLOOKUP(A171,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24502,7 +24756,7 @@
       </c>
       <c r="AS171" s="71">
         <f t="shared" si="8"/>
-        <v>3.4933792890511306</v>
+        <v>3.4978237334955722</v>
       </c>
     </row>
     <row r="172" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24590,7 +24844,9 @@
       <c r="AB172" s="56">
         <v>27.1</v>
       </c>
-      <c r="AC172" s="56"/>
+      <c r="AC172" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AD172" s="56"/>
       <c r="AE172" s="56"/>
       <c r="AF172" s="56"/>
@@ -24605,11 +24861,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>26.286111111111115</v>
+        <v>26.276315789473689</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24617,7 +24873,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>1.7804343462546761</v>
+        <v>1.7706390246172496</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24705,7 +24961,9 @@
       <c r="AB173" s="56">
         <v>26.35</v>
       </c>
-      <c r="AC173" s="56"/>
+      <c r="AC173" s="56">
+        <v>26.75</v>
+      </c>
       <c r="AD173" s="56"/>
       <c r="AE173" s="56"/>
       <c r="AF173" s="56"/>
@@ -24720,11 +24978,11 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>25.947222222222223</v>
+        <v>25.989473684210527</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24732,7 +24990,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>1.9333129789272121</v>
+        <v>1.975564440915516</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24869,23 +25127,45 @@
         <v>25.4</v>
       </c>
       <c r="N175" s="56"/>
-      <c r="O175" s="56"/>
-      <c r="P175" s="56"/>
-      <c r="Q175" s="56"/>
-      <c r="R175" s="56"/>
-      <c r="S175" s="56"/>
+      <c r="O175" s="56">
+        <v>26.2</v>
+      </c>
+      <c r="P175" s="56">
+        <v>25.733333333333331</v>
+      </c>
+      <c r="Q175" s="56">
+        <v>24.2</v>
+      </c>
+      <c r="R175" s="56">
+        <v>25.066666666666659</v>
+      </c>
+      <c r="S175" s="56">
+        <v>25.4</v>
+      </c>
       <c r="T175" s="56">
         <v>25.6</v>
       </c>
       <c r="U175" s="56">
         <v>24.933333333333341</v>
       </c>
-      <c r="V175" s="56"/>
-      <c r="W175" s="56"/>
-      <c r="X175" s="56"/>
-      <c r="Y175" s="56"/>
-      <c r="Z175" s="56"/>
-      <c r="AA175" s="56"/>
+      <c r="V175" s="56">
+        <v>24.93333333333333</v>
+      </c>
+      <c r="W175" s="56">
+        <v>26.4</v>
+      </c>
+      <c r="X175" s="56">
+        <v>24.6</v>
+      </c>
+      <c r="Y175" s="56">
+        <v>25.86666666666666</v>
+      </c>
+      <c r="Z175" s="56">
+        <v>25.466666666666669</v>
+      </c>
+      <c r="AA175" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AB175" s="56"/>
       <c r="AC175" s="56"/>
       <c r="AD175" s="56"/>
@@ -24902,19 +25182,19 @@
       <c r="AO175" s="56"/>
       <c r="AP175" s="58">
         <f t="shared" si="6"/>
-        <v>5</v>
-      </c>
-      <c r="AQ175" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ175" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>25.287499999999998</v>
       </c>
       <c r="AR175" s="71">
         <f>IFERROR(VLOOKUP(A175,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>23.699565695841741</v>
       </c>
-      <c r="AS175" s="71" t="str">
+      <c r="AS175" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.5879343041582565</v>
       </c>
     </row>
     <row r="176" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25152,7 +25432,9 @@
       <c r="AB178" s="56">
         <v>26.8</v>
       </c>
-      <c r="AC178" s="56"/>
+      <c r="AC178" s="56">
+        <v>25.933333333333341</v>
+      </c>
       <c r="AD178" s="56"/>
       <c r="AE178" s="56"/>
       <c r="AF178" s="56"/>
@@ -25167,19 +25449,19 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ178" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>25.720000000000002</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.463062760640639</v>
       </c>
-      <c r="AS178" s="71" t="str">
+      <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.2569372393593632</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25267,7 +25549,9 @@
       <c r="AB179" s="56">
         <v>19.850000000000001</v>
       </c>
-      <c r="AC179" s="56"/>
+      <c r="AC179" s="56">
+        <v>18.8</v>
+      </c>
       <c r="AD179" s="56"/>
       <c r="AE179" s="56"/>
       <c r="AF179" s="56"/>
@@ -25282,11 +25566,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>18.924999999999997</v>
+        <v>18.918421052631579</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25294,7 +25578,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>1.6782374735098955</v>
+        <v>1.6716585261414778</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25720,7 +26004,9 @@
       </c>
       <c r="AA184" s="56"/>
       <c r="AB184" s="56"/>
-      <c r="AC184" s="56"/>
+      <c r="AC184" s="56">
+        <v>31.93333333333333</v>
+      </c>
       <c r="AD184" s="56"/>
       <c r="AE184" s="56"/>
       <c r="AF184" s="56"/>
@@ -25735,7 +26021,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -26100,7 +26386,9 @@
       <c r="AB188" s="56">
         <v>19.733333333333331</v>
       </c>
-      <c r="AC188" s="56"/>
+      <c r="AC188" s="56">
+        <v>18.2</v>
+      </c>
       <c r="AD188" s="56"/>
       <c r="AE188" s="56"/>
       <c r="AF188" s="56"/>
@@ -26115,11 +26403,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>18.176470588235293</v>
+        <v>18.177777777777777</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26127,7 +26415,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.9637644191383643</v>
+        <v>1.965071608680848</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26201,7 +26489,9 @@
       </c>
       <c r="AA189" s="56"/>
       <c r="AB189" s="56"/>
-      <c r="AC189" s="56"/>
+      <c r="AC189" s="56">
+        <v>35.066666666666663</v>
+      </c>
       <c r="AD189" s="56"/>
       <c r="AE189" s="56"/>
       <c r="AF189" s="56"/>
@@ -26216,7 +26506,7 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ189" s="71" t="str">
         <f t="shared" si="7"/>
@@ -26312,7 +26602,9 @@
       <c r="AB190" s="56">
         <v>32.533333333333331</v>
       </c>
-      <c r="AC190" s="56"/>
+      <c r="AC190" s="56">
+        <v>33.200000000000003</v>
+      </c>
       <c r="AD190" s="56"/>
       <c r="AE190" s="56"/>
       <c r="AF190" s="56"/>
@@ -26327,11 +26619,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>31.395833333333329</v>
+        <v>31.501960784313724</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26339,7 +26631,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>2.3275827544103791</v>
+        <v>2.4337102053907742</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26427,7 +26719,9 @@
       <c r="AB191" s="56">
         <v>21</v>
       </c>
-      <c r="AC191" s="56"/>
+      <c r="AC191" s="56">
+        <v>19.399999999999999</v>
+      </c>
       <c r="AD191" s="56"/>
       <c r="AE191" s="56"/>
       <c r="AF191" s="56"/>
@@ -26442,11 +26736,11 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ191" s="71">
         <f t="shared" si="7"/>
-        <v>19.538888888888888</v>
+        <v>19.53157894736842</v>
       </c>
       <c r="AR191" s="71">
         <f>IFERROR(VLOOKUP(A191,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26454,7 +26748,7 @@
       </c>
       <c r="AS191" s="71">
         <f t="shared" si="8"/>
-        <v>2.1049833380145664</v>
+        <v>2.0976733964940983</v>
       </c>
     </row>
     <row r="192" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26542,7 +26836,9 @@
       <c r="AB192" s="56">
         <v>29.466666666666669</v>
       </c>
-      <c r="AC192" s="56"/>
+      <c r="AC192" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AD192" s="56"/>
       <c r="AE192" s="56"/>
       <c r="AF192" s="56"/>
@@ -26557,11 +26853,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>26.762962962962963</v>
+        <v>26.785964912280701</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26569,7 +26865,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>1.2609626436782015</v>
+        <v>1.2839645929959396</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26764,7 +27060,9 @@
       <c r="AB194" s="56">
         <v>24.13333333333334</v>
       </c>
-      <c r="AC194" s="56"/>
+      <c r="AC194" s="56">
+        <v>22.06666666666667</v>
+      </c>
       <c r="AD194" s="56"/>
       <c r="AE194" s="56"/>
       <c r="AF194" s="56"/>
@@ -26779,11 +27077,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>22.788235294117644</v>
+        <v>22.748148148148147</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26791,7 +27089,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>0.7290691362015238</v>
+        <v>0.68898199023202622</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26865,7 +27163,9 @@
       <c r="AB195" s="56">
         <v>30.6</v>
       </c>
-      <c r="AC195" s="56"/>
+      <c r="AC195" s="56">
+        <v>27.733333333333331</v>
+      </c>
       <c r="AD195" s="56"/>
       <c r="AE195" s="56"/>
       <c r="AF195" s="56"/>
@@ -26880,7 +27180,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -26980,7 +27280,9 @@
       <c r="AB196" s="56">
         <v>25.06666666666667</v>
       </c>
-      <c r="AC196" s="56"/>
+      <c r="AC196" s="56">
+        <v>21.533333333333331</v>
+      </c>
       <c r="AD196" s="56"/>
       <c r="AE196" s="56"/>
       <c r="AF196" s="56"/>
@@ -26995,11 +27297,11 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v>23.266666666666666</v>
+        <v>23.17543859649123</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27007,7 +27309,7 @@
       </c>
       <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v>3.200560078985756</v>
+        <v>3.1093320088103198</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27095,7 +27397,9 @@
       <c r="AB197" s="56">
         <v>29.4</v>
       </c>
-      <c r="AC197" s="56"/>
+      <c r="AC197" s="56">
+        <v>29.066666666666659</v>
+      </c>
       <c r="AD197" s="56"/>
       <c r="AE197" s="56"/>
       <c r="AF197" s="56"/>
@@ -27109,20 +27413,20 @@
       <c r="AN197" s="56"/>
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
-        <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>18</v>
+        <f t="shared" ref="AP197:AP212" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
+        <v>19</v>
       </c>
       <c r="AQ197" s="71">
-        <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>27.922222222222224</v>
+        <f t="shared" ref="AQ197:AQ212" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
+        <v>27.982456140350877</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>24.80996849865301</v>
       </c>
       <c r="AS197" s="71">
-        <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>3.1122537235692143</v>
+        <f t="shared" ref="AS197:AS212" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
+        <v>3.1724876416978667</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27210,7 +27514,9 @@
       <c r="AB198" s="56">
         <v>23.9</v>
       </c>
-      <c r="AC198" s="56"/>
+      <c r="AC198" s="56">
+        <v>24.1</v>
+      </c>
       <c r="AD198" s="56"/>
       <c r="AE198" s="56"/>
       <c r="AF198" s="56"/>
@@ -27225,11 +27531,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>22.61944444444444</v>
+        <v>22.69736842105263</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27325,7 +27631,9 @@
       <c r="AB199" s="56">
         <v>17.733333333333331</v>
       </c>
-      <c r="AC199" s="56"/>
+      <c r="AC199" s="56">
+        <v>17.666666666666671</v>
+      </c>
       <c r="AD199" s="56"/>
       <c r="AE199" s="56"/>
       <c r="AF199" s="56"/>
@@ -27340,11 +27648,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.985185185185188</v>
+        <v>17.02105263157895</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27352,7 +27660,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.90400925116243869</v>
+        <v>0.93987669755620118</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27436,7 +27744,9 @@
         <v>15.9</v>
       </c>
       <c r="AB200" s="56"/>
-      <c r="AC200" s="56"/>
+      <c r="AC200" s="56">
+        <v>13.55</v>
+      </c>
       <c r="AD200" s="56"/>
       <c r="AE200" s="56"/>
       <c r="AF200" s="56"/>
@@ -27451,11 +27761,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>14.765625</v>
+        <v>14.694117647058825</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27463,7 +27773,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.4552662118874302</v>
+        <v>1.3837588589462548</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27551,7 +27861,9 @@
       <c r="AB201" s="56">
         <v>30.55</v>
       </c>
-      <c r="AC201" s="56"/>
+      <c r="AC201" s="56">
+        <v>29.6</v>
+      </c>
       <c r="AD201" s="56"/>
       <c r="AE201" s="56"/>
       <c r="AF201" s="56"/>
@@ -27566,11 +27878,11 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ201" s="71">
         <f t="shared" si="10"/>
-        <v>29.358333333333331</v>
+        <v>29.371052631578944</v>
       </c>
       <c r="AR201" s="71">
         <f>IFERROR(VLOOKUP(A201,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27578,7 +27890,7 @@
       </c>
       <c r="AS201" s="71">
         <f t="shared" si="11"/>
-        <v>2.9618466434941624</v>
+        <v>2.9745659417397761</v>
       </c>
     </row>
     <row r="202" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27663,8 +27975,12 @@
       <c r="AA202" s="56">
         <v>13.1</v>
       </c>
-      <c r="AB202" s="56"/>
-      <c r="AC202" s="56"/>
+      <c r="AB202" s="56">
+        <v>11.75</v>
+      </c>
+      <c r="AC202" s="56">
+        <v>13.025</v>
+      </c>
       <c r="AD202" s="56"/>
       <c r="AE202" s="56"/>
       <c r="AF202" s="56"/>
@@ -27679,11 +27995,11 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ202" s="71">
         <f t="shared" si="10"/>
-        <v>13.294117647058824</v>
+        <v>13.198684210526316</v>
       </c>
       <c r="AR202" s="71">
         <f>IFERROR(VLOOKUP(A202,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27691,7 +28007,7 @@
       </c>
       <c r="AS202" s="71">
         <f t="shared" si="11"/>
-        <v>0.20432300528580427</v>
+        <v>0.10888956875329647</v>
       </c>
     </row>
     <row r="203" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27973,7 +28289,9 @@
       <c r="AB205" s="56">
         <v>15.45</v>
       </c>
-      <c r="AC205" s="56"/>
+      <c r="AC205" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AD205" s="56"/>
       <c r="AE205" s="56"/>
       <c r="AF205" s="56"/>
@@ -27988,11 +28306,11 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>15.469444444444441</v>
+        <v>15.423684210526313</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28000,7 +28318,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.8034552602171114</v>
+        <v>1.7576950262989826</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28088,7 +28406,9 @@
       <c r="AB206" s="56">
         <v>14.85</v>
       </c>
-      <c r="AC206" s="56"/>
+      <c r="AC206" s="56">
+        <v>13.85</v>
+      </c>
       <c r="AD206" s="56"/>
       <c r="AE206" s="56"/>
       <c r="AF206" s="56"/>
@@ -28103,11 +28423,11 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ206" s="71">
         <f t="shared" si="10"/>
-        <v>13.744444444444447</v>
+        <v>13.750000000000004</v>
       </c>
       <c r="AR206" s="71" t="str">
         <f>IFERROR(VLOOKUP(A206,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28312,7 +28632,9 @@
       <c r="AB208" s="56">
         <v>13.6</v>
       </c>
-      <c r="AC208" s="56"/>
+      <c r="AC208" s="56">
+        <v>15.65</v>
+      </c>
       <c r="AD208" s="56"/>
       <c r="AE208" s="56"/>
       <c r="AF208" s="56"/>
@@ -28327,11 +28649,11 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>14.071296296296294</v>
+        <v>14.154385964912278</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28427,7 +28749,9 @@
       <c r="AB209" s="56">
         <v>10.95</v>
       </c>
-      <c r="AC209" s="56"/>
+      <c r="AC209" s="56">
+        <v>10.75</v>
+      </c>
       <c r="AD209" s="56"/>
       <c r="AE209" s="56"/>
       <c r="AF209" s="56"/>
@@ -28442,11 +28766,11 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.127777777777776</v>
+        <v>11.107894736842104</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28653,7 +28977,9 @@
       <c r="AB211" s="56">
         <v>8.1</v>
       </c>
-      <c r="AC211" s="56"/>
+      <c r="AC211" s="56">
+        <v>8.8500000000000014</v>
+      </c>
       <c r="AD211" s="56"/>
       <c r="AE211" s="56"/>
       <c r="AF211" s="56"/>
@@ -28668,11 +28994,11 @@
       <c r="AO211" s="56"/>
       <c r="AP211" s="58">
         <f t="shared" si="9"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ211" s="71">
         <f t="shared" si="10"/>
-        <v>8.5083333333333329</v>
+        <v>8.526315789473685</v>
       </c>
       <c r="AR211" s="71">
         <f>IFERROR(VLOOKUP(A211,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28680,7 +29006,7 @@
       </c>
       <c r="AS211" s="71">
         <f t="shared" si="11"/>
-        <v>0.143637887111705</v>
+        <v>0.1616203432520571</v>
       </c>
     </row>
     <row r="212" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -28765,8 +29091,12 @@
       <c r="AA212" s="56">
         <v>26.45</v>
       </c>
-      <c r="AB212" s="56"/>
-      <c r="AC212" s="56"/>
+      <c r="AB212" s="56">
+        <v>26.5</v>
+      </c>
+      <c r="AC212" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AD212" s="56"/>
       <c r="AE212" s="56"/>
       <c r="AF212" s="56"/>
@@ -28781,11 +29111,11 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v>28.291176470588237</v>
+        <v>28.055263157894739</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
